--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571430581</v>
+        <v>46157.93108965232</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108965232</v>
+        <v>46157.93178189435</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178189435</v>
+        <v>46157.93403003814</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403003814</v>
+        <v>46157.9372098407</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372098407</v>
+        <v>46158.28219031524</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219031524</v>
+        <v>46158.29693548222</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29693548222</v>
+        <v>46158.29818207741</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29818207741</v>
+        <v>46158.3339001182</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339001182</v>
+        <v>46158.36859855548</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859855548</v>
+        <v>46158.37290452793</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
